--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jarod\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jarod\Desktop\sjarod.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0DF63EF-ADDC-43C8-8C63-36E81294F86E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AECE1B71-01DF-42D6-BEE1-0C2190A9A429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{16C9B547-A0B7-45C0-B721-251715838CB6}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{16C9B547-A0B7-45C0-B721-251715838CB6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="342">
   <si>
     <t>Game Programming 1</t>
   </si>
@@ -650,15 +650,9 @@
     <t>A.4 : Mise au point de l'interactivité utilisateurs</t>
   </si>
   <si>
-    <t>demonstration du jeu sur PS4</t>
-  </si>
-  <si>
     <t>playtest du FPS developpe</t>
   </si>
   <si>
-    <t>playtest du TPS developpe</t>
-  </si>
-  <si>
     <t>demonstration du gain de performance avec l'aide de plusieurs builds avec des parametrages differents</t>
   </si>
   <si>
@@ -677,9 +671,6 @@
     <t>developpement d'un jeu avec le moteur</t>
   </si>
   <si>
-    <t>playtest de celui ci\</t>
-  </si>
-  <si>
     <t>Expérience professionnelles</t>
   </si>
   <si>
@@ -767,20 +758,317 @@
     <t>bibliotheque permettant l'utilisation de plusieurs API graphique</t>
   </si>
   <si>
-    <t>ray marcher pour afficher de la lumiere volumetrique en GLSL sur Shadertoy</t>
-  </si>
-  <si>
     <t>technique permettant d'afficher des soft shadows avec un ray marcher en GLSL sur Shadertoy</t>
   </si>
   <si>
     <t>realisation d'une bibliotheque modulaire de rendu graphique (iteration sur l'architecture)</t>
+  </si>
+  <si>
+    <t>A.1 : Veille technologique</t>
+  </si>
+  <si>
+    <t>A.2 : Choix de la plateforme 3D</t>
+  </si>
+  <si>
+    <t>A.3 : Paramétrage</t>
+  </si>
+  <si>
+    <t>A.1 : Mise au point du cahier des charges</t>
+  </si>
+  <si>
+    <t>A.2 : Séquençage et allocation des ressources nécessaires</t>
+  </si>
+  <si>
+    <t>A.3 : Pilotage de la réalisation</t>
+  </si>
+  <si>
+    <t>A.1 : Analyse compétences</t>
+  </si>
+  <si>
+    <t>A.2 : Répartition des tâches</t>
+  </si>
+  <si>
+    <t>A.3 : Choix et mise en oeuvre des outils collaboratifs</t>
+  </si>
+  <si>
+    <t>A.4 : Animation des équipes créatives et techniques</t>
+  </si>
+  <si>
+    <t>A.5 : Prise en compte des situations de handicap</t>
+  </si>
+  <si>
+    <t>playtest du TPS développé</t>
+  </si>
+  <si>
+    <t>démonstration du jeu sur PS4</t>
+  </si>
+  <si>
+    <t>découverte du Kit de Développement PS4</t>
+  </si>
+  <si>
+    <t>playtest de celui ci</t>
+  </si>
+  <si>
+    <t>utilisation de nouvelles API et bibliothèques telles que Assimp, Cmake, Jolt Physics, Tracy</t>
+  </si>
+  <si>
+    <t>OpenGL, GLFW et Dear ImGui sont les outils 3D séléctionné en raison de leur simplicité</t>
+  </si>
+  <si>
+    <t>mécanique de mouvement de orbital</t>
+  </si>
+  <si>
+    <t>découverte du Kit de Développement Nintendo Switch</t>
+  </si>
+  <si>
+    <t>choix entre un HTN, un GOAP ou du Deep Q-Learning</t>
+  </si>
+  <si>
+    <t>recherche sur la simulation de fluide "Stable Fluid" et comparaison avec une technique basé sur des Shaders</t>
+  </si>
+  <si>
+    <t>comparaison entre un HTN et un GOAP</t>
+  </si>
+  <si>
+    <t>recherche sur diverse technique pour charger une carte de manière invisible</t>
+  </si>
+  <si>
+    <t>implementation d'une fonctionnalité de slow motion : recherche sur les differents moyens de l'atteindre</t>
+  </si>
+  <si>
+    <t>recherche sur les differents outils mis en place par Unreal Engine pour automatiser les builds du jeu et du moteur</t>
+  </si>
+  <si>
+    <t>recherche pour reproduire au mieux des transitions fluides entre menus, cinématiques, et jeu ; comparaison avec ce qui est fait dans le milieu</t>
+  </si>
+  <si>
+    <t>recherche sur l'utilisation du Gameplay Ability System</t>
+  </si>
+  <si>
+    <t>choix de l'API graphique (OpenGL, Vulkan, DirectX)</t>
+  </si>
+  <si>
+    <t>choix des differents algorithmes de Global Illumination implémentable</t>
+  </si>
+  <si>
+    <t>https://github.com/SJarod/radiance-playground</t>
+  </si>
+  <si>
+    <t>recherche sur differentes methodes pour voir le joueur a travers les murs lorsque la camera est imobile (dans le cas d'un Top Down View)</t>
+  </si>
+  <si>
+    <t>travail de recherche sur differentes façons de réaliser une RHI</t>
+  </si>
+  <si>
+    <t>découverte du Ray Marching pour le rendu de volume</t>
+  </si>
+  <si>
+    <t>veille sur differents type de Player Controllers existant dans les jeux vidéo</t>
+  </si>
+  <si>
+    <t>selection du codex video le plus adapté pour un projet de recherche et une implementation rapide/efficace (H.264)</t>
+  </si>
+  <si>
+    <t>le projet cible est un jeu sur Windows mais le moteur développé ainsi que le jeu doit être compatible avec Linux</t>
+  </si>
+  <si>
+    <t>le moteur Unity est choisi pour faciliter le developpement d'une architecture utilisable sur une semaine</t>
+  </si>
+  <si>
+    <t>Unreal Engine 5 est utilisé pour mieux convenir aux performance de la PS5, une passe de recherche sur les capacité s du moteur et de la console a été effectué, notamment pour l'utilisation du Ray Tracing</t>
+  </si>
+  <si>
+    <t>Vulkan est l'API choisit en raison de sa flexibilité et de la possibilité d'implementer plusieurs fonctionnalités permettant d'avoir le plus de controle sur notre application (comme la gestion de la memoire et la possibilité de faire des compute shaders)</t>
+  </si>
+  <si>
+    <t>veille sur une architecture extensible qui se base sur ce qui est fait dans le milieu, dans les moteurs de jeu (render graph)</t>
+  </si>
+  <si>
+    <t>le projet principal de l'entreprise ayant pour objectif de migrer vers Vulkan, cette API est utilisé pour le projet annexe de recherche sur le decodage video avec acceleration materielle</t>
+  </si>
+  <si>
+    <t>Shadertoy est utilisé pour sa fiabilité</t>
+  </si>
+  <si>
+    <t>utilisation de OpenGL pour la gestion de ressources necessaire au rendu 3D</t>
+  </si>
+  <si>
+    <t>developpement d'un moteur de rendu supportant l'animation squelettique</t>
+  </si>
+  <si>
+    <t>utilisation des fichiers de config de Unreal Engine pour obtenir un rendu plus optimisé en fonction de la plateforme cible (Windows et PS5)</t>
+  </si>
+  <si>
+    <t>utilisation des differentes options données par Unreal Engine pour obtenir un rendu plus optimisé</t>
+  </si>
+  <si>
+    <t>utilisation des Render Pass Vulkan pour respecter le rendu classique Vulkan</t>
+  </si>
+  <si>
+    <t>utilsation de l'extension Dynamic Rendering pour augmenter la vitesse de developpement</t>
+  </si>
+  <si>
+    <t>description des objectifs primaires (animation, toon shading, shadow mapping)</t>
+  </si>
+  <si>
+    <t>definition du scope : simple surface interactible</t>
+  </si>
+  <si>
+    <t>augmenter la frequence d'image sans baisser la qualité visuelle : 90 fps</t>
+  </si>
+  <si>
+    <t>maximiser l'utilisation des performances de la PS5 en utilisant les nouvelles technologie (Lumen, Nanite)</t>
+  </si>
+  <si>
+    <t>obtenir un temps de chargement invisible</t>
+  </si>
+  <si>
+    <t>obtenir un rendu credible de Global Illumination avec au moins deux algorithms (Radiance Cascades et GI With Irradiance Probes)</t>
+  </si>
+  <si>
+    <t>decoder une video donner par l'entreprise (par les clients) avec la carte graphique</t>
+  </si>
+  <si>
+    <t>le module de decodage doit etre assez modulaire pour etre integrer dans le moteur principal facilement</t>
+  </si>
+  <si>
+    <t>ameliorer le game feel d'un personnage en top down</t>
+  </si>
+  <si>
+    <t>determiner les cas d'utilisation d'une plateforme web</t>
+  </si>
+  <si>
+    <t>realiser une RHI modulaire permettant d'y imbriquer n'importe quel implementation (du client) ou n'importe quel API graphique</t>
+  </si>
+  <si>
+    <t>repartition du travail entre tout les membres du groupe (editeur, rendu, physic, gameplay)</t>
+  </si>
+  <si>
+    <t>repartition du travail (gameplay, physic, rendu, architecture)</t>
+  </si>
+  <si>
+    <t>decoupage en plusieurs paliers (milestones), chaque etape decrit une amelioration au niveau du gameplay, de l'interface utilisateur ou des performances</t>
+  </si>
+  <si>
+    <t>reunions avec l'equipe entiere</t>
+  </si>
+  <si>
+    <t>reunions avec l'equipe chargee de la programmation</t>
+  </si>
+  <si>
+    <t>reunions avec les differents corps de metiers directement affecte par la tache actuelle</t>
+  </si>
+  <si>
+    <t>utilisation d'outils de gestion de projets tel que jira</t>
+  </si>
+  <si>
+    <t>decoupage du projet en milestone et en sous etape avant d'obtenir le resultat final</t>
+  </si>
+  <si>
+    <t>organisation de la production et discussion des etapes avec le maitre de stage</t>
+  </si>
+  <si>
+    <t>reunion hebdomadaires</t>
+  </si>
+  <si>
+    <t>discussions entre membres d'equipe</t>
+  </si>
+  <si>
+    <t>discussions avec les mentors</t>
+  </si>
+  <si>
+    <t>A.4 : Tests et mise en production</t>
+  </si>
+  <si>
+    <t>application des changements majeurs sur une scene de test</t>
+  </si>
+  <si>
+    <t>creation de prototype pour attester de la bonne fonctionnalité de chaque implementation (slow motion, chargement de niveaux)</t>
+  </si>
+  <si>
+    <t>tests sur une autre plateforme (Shadertoy)</t>
+  </si>
+  <si>
+    <t>points d'avancement avec le maitre de stage</t>
+  </si>
+  <si>
+    <t>utilisation de la RHI pour attester de sa bonne architecture</t>
+  </si>
+  <si>
+    <t>utilisation des outils d'automation de Unreal Engine</t>
+  </si>
+  <si>
+    <t>creation de plugins sous Unreal Engine</t>
+  </si>
+  <si>
+    <t>lecture de specification ISO</t>
+  </si>
+  <si>
+    <t>decodage video logiciel via des bitstreams</t>
+  </si>
+  <si>
+    <t>utilisation de l'API Vulkan avec une architecture de Render Graph</t>
+  </si>
+  <si>
+    <t>utilisation d'une pipeline de rendu classique ainsi qu'une pipeline compute</t>
+  </si>
+  <si>
+    <t>collaboration avec differents corps de metier en fonction des taches assignees</t>
+  </si>
+  <si>
+    <t>assignation des roles de chacun</t>
+  </si>
+  <si>
+    <t>role axés sur l'etude des performances d'un jeu sous Unreal Engine</t>
+  </si>
+  <si>
+    <t>mise en place d'outils pour permettre a l'equipe de build sur leur pc personnel</t>
+  </si>
+  <si>
+    <t>gestion des taches dans un tableau kanban</t>
+  </si>
+  <si>
+    <t>utilisation d'un tableau kanban</t>
+  </si>
+  <si>
+    <t>mise en place et utilisation de backlogs</t>
+  </si>
+  <si>
+    <t>mise en place d'outils pour faciliter l'integration des artistes</t>
+  </si>
+  <si>
+    <t>post mortem au sein de l'equipe programmeur</t>
+  </si>
+  <si>
+    <t>post mortem dans toute l'equipe</t>
+  </si>
+  <si>
+    <t>recherches sur le Ray Marching pour afficher de la lumiere volumetrique en GLSL sur Shadertoy</t>
+  </si>
+  <si>
+    <t>recherche sur l'algorithme GJK</t>
+  </si>
+  <si>
+    <t>recherches sur diverses techniques de Global Illumination (Radiance Cascades)</t>
+  </si>
+  <si>
+    <t>recherches sur l'architecture d'une bibliothèque de rendu</t>
+  </si>
+  <si>
+    <t>comparaison du visuel avec les rendus trouvés dans les papiers de recherches servant de references</t>
+  </si>
+  <si>
+    <t>prototype sur Shadertoy avant de passer a l'implementation sur le moteur dedié</t>
+  </si>
+  <si>
+    <t>reunions entre equipiers et avec les producers</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -794,13 +1082,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -812,14 +1114,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1152,17 +1457,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0FD204F-2399-4498-A879-12600FE66628}">
-  <dimension ref="A1:M171"/>
+  <dimension ref="A1:W176"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="9.140625" customWidth="1"/>
-    <col min="4" max="5" width="9.140625" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="6" width="9.140625" customWidth="1"/>
-    <col min="7" max="9" width="9.140625" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="13" width="9.140625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="33.7109375" customWidth="1"/>
+    <col min="3" max="3" width="21.28515625" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="18.85546875" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="20.5703125" customWidth="1"/>
+    <col min="7" max="7" width="23.7109375" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="18.85546875" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="15.7109375" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="18.85546875" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="18.7109375" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="18.85546875" customWidth="1"/>
+    <col min="14" max="14" width="18.140625" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="15" width="18.7109375" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="16" width="14.85546875" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="17" width="17.28515625" customWidth="1"/>
+    <col min="18" max="18" width="18.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="19.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="21" width="16.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="22" max="22" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>174</v>
       </c>
@@ -1178,17 +1499,17 @@
       <c r="J1" t="s">
         <v>142</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>143</v>
       </c>
-      <c r="L1" t="s">
+      <c r="Q1" t="s">
         <v>144</v>
       </c>
-      <c r="M1" t="s">
+      <c r="W1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
         <v>171</v>
       </c>
@@ -1210,474 +1531,519 @@
       <c r="I2" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J2" t="s">
+        <v>242</v>
+      </c>
+      <c r="K2" t="s">
+        <v>243</v>
+      </c>
+      <c r="L2" t="s">
+        <v>244</v>
+      </c>
+      <c r="M2" t="s">
+        <v>245</v>
+      </c>
+      <c r="N2" t="s">
+        <v>246</v>
+      </c>
+      <c r="O2" t="s">
+        <v>247</v>
+      </c>
+      <c r="P2" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>248</v>
+      </c>
+      <c r="R2" t="s">
+        <v>249</v>
+      </c>
+      <c r="S2" t="s">
+        <v>250</v>
+      </c>
+      <c r="T2" t="s">
+        <v>251</v>
+      </c>
+      <c r="U2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>139</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="W5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M6" t="s">
+    <row r="6" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>140</v>
       </c>
-      <c r="M8" t="s">
+      <c r="W8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>146</v>
       </c>
-      <c r="M11" t="s">
+      <c r="W11" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>145</v>
       </c>
-      <c r="M12" t="s">
+      <c r="W12" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M14" t="s">
+    <row r="14" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W14" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M15" t="s">
+    <row r="15" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M17" t="s">
+    <row r="17" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W17" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M18" t="s">
+    <row r="18" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W18" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="19" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M20" t="s">
+    <row r="20" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W20" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M21" t="s">
+    <row r="21" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W21" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M23" t="s">
+    <row r="23" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M24" t="s">
+    <row r="24" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W24" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
         <v>147</v>
       </c>
-      <c r="M26" t="s">
+      <c r="W26" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M28" t="s">
+    <row r="28" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W28" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M29" t="s">
+    <row r="29" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W29" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M31" t="s">
+    <row r="31" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W31" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="32" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M32" t="s">
+    <row r="32" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W32" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="33" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M34" t="s">
+    <row r="34" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W34" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="35" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M35" t="s">
+    <row r="35" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W35" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M37" t="s">
+    <row r="37" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W37" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="38" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M38" t="s">
+    <row r="38" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W38" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="39" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
         <v>148</v>
       </c>
-      <c r="M40" t="s">
+      <c r="W40" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="41" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M41" t="s">
+    <row r="41" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W41" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="42" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
         <v>149</v>
       </c>
-      <c r="M43" t="s">
+      <c r="W43" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="44" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M44" t="s">
+    <row r="44" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W44" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="45" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="C46" t="s">
         <v>150</v>
       </c>
-      <c r="M46" t="s">
+      <c r="W46" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M47" t="s">
+    <row r="47" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W47" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="48" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="I49" t="s">
-        <v>205</v>
-      </c>
-      <c r="M49" t="s">
+        <v>204</v>
+      </c>
+      <c r="N49" t="s">
+        <v>302</v>
+      </c>
+      <c r="O49" t="s">
+        <v>310</v>
+      </c>
+      <c r="W49" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="50" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M50" t="s">
+    <row r="50" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W50" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M53" t="s">
+    <row r="53" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W53" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="54" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M54" t="s">
+    <row r="54" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W54" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="55" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="56" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M56" t="s">
+    <row r="56" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W56" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="57" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M57" t="s">
+    <row r="57" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W57" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="58" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="59" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="C59" t="s">
         <v>151</v>
       </c>
-      <c r="M59" t="s">
+      <c r="W59" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M60" t="s">
+    <row r="60" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W60" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="61" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="62" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="C62" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="63" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="64" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="C64" t="s">
         <v>153</v>
       </c>
-      <c r="M64" t="s">
+      <c r="W64" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="65" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M65" t="s">
+    <row r="65" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W65" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="66" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="67" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="C67" t="s">
         <v>154</v>
       </c>
-      <c r="M67" t="s">
+      <c r="W67" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="68" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M68" t="s">
+    <row r="68" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W68" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="69" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="70" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="C70" t="s">
         <v>156</v>
       </c>
       <c r="I70" t="s">
-        <v>206</v>
-      </c>
-      <c r="M70" t="s">
+        <v>253</v>
+      </c>
+      <c r="J70" t="s">
+        <v>255</v>
+      </c>
+      <c r="W70" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="71" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="I71" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="72" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="73" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M73" t="s">
+    <row r="73" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W73" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="74" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M74" t="s">
+    <row r="74" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W74" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="75" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="76" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M76" t="s">
+    <row r="76" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W76" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="77" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M77" t="s">
+    <row r="77" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W77" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="78" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="79" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="C79" t="s">
         <v>157</v>
       </c>
-      <c r="M79" t="s">
+      <c r="W79" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="80" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="C80" t="s">
         <v>158</v>
       </c>
-      <c r="M80" t="s">
+      <c r="W80" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="81" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="C81" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="82" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="83" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="C83" t="s">
         <v>160</v>
       </c>
-      <c r="M83" t="s">
+      <c r="W83" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="84" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M84" t="s">
+    <row r="84" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W84" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="85" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="86" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="C86" t="s">
         <v>161</v>
       </c>
@@ -1697,13 +2063,31 @@
         <v>200</v>
       </c>
       <c r="I86" t="s">
-        <v>212</v>
+        <v>210</v>
+      </c>
+      <c r="J86" t="s">
+        <v>257</v>
+      </c>
+      <c r="K86" t="s">
+        <v>258</v>
+      </c>
+      <c r="L86" t="s">
+        <v>284</v>
       </c>
       <c r="M86" t="s">
+        <v>301</v>
+      </c>
+      <c r="R86" t="s">
+        <v>326</v>
+      </c>
+      <c r="S86" t="s">
+        <v>329</v>
+      </c>
+      <c r="W86" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="87" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="C87" t="s">
         <v>162</v>
       </c>
@@ -1711,161 +2095,182 @@
         <v>178</v>
       </c>
       <c r="I87" t="s">
-        <v>213</v>
+        <v>256</v>
+      </c>
+      <c r="K87" t="s">
+        <v>277</v>
+      </c>
+      <c r="L87" t="s">
+        <v>285</v>
       </c>
       <c r="M87" t="s">
+        <v>290</v>
+      </c>
+      <c r="W87" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="88" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="C88" t="s">
         <v>163</v>
       </c>
-      <c r="M88" t="s">
+      <c r="W88" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="89" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="C89" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="92" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M92" t="s">
+    <row r="92" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="J92" t="s">
+        <v>259</v>
+      </c>
+      <c r="K92" t="s">
+        <v>278</v>
+      </c>
+      <c r="W92" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="93" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M93" t="s">
+    <row r="93" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W93" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="94" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="95" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="D95" t="s">
         <v>184</v>
       </c>
-      <c r="M95" t="s">
+      <c r="W95" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="96" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M96" t="s">
+    <row r="96" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W96" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="97" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="98" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M98" t="s">
+    <row r="98" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W98" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="99" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M100" t="s">
+    <row r="100" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W100" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="101" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M101" t="s">
+    <row r="101" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W101" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="102" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="103" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="C103" t="s">
         <v>165</v>
       </c>
       <c r="D103" t="s">
         <v>182</v>
       </c>
-      <c r="M103" t="s">
+      <c r="J103" t="s">
+        <v>260</v>
+      </c>
+      <c r="W103" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="104" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="105" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M105" t="s">
+    <row r="105" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W105" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="106" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M106" t="s">
+    <row r="106" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W106" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="107" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="108" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="D108" t="s">
         <v>179</v>
       </c>
       <c r="I108" t="s">
-        <v>209</v>
-      </c>
-      <c r="M108" t="s">
+        <v>207</v>
+      </c>
+      <c r="W108" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="109" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="110" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M110" t="s">
+    <row r="110" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W110" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="111" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="112" spans="2:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M112" t="s">
+    <row r="112" spans="2:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="J112" t="s">
+        <v>261</v>
+      </c>
+      <c r="W112" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="113" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="114" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="D114" t="s">
         <v>181</v>
       </c>
@@ -1881,59 +2286,68 @@
       <c r="H114" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="115" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="J114" t="s">
+        <v>262</v>
+      </c>
+      <c r="M114" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="116" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="I116" t="s">
-        <v>208</v>
-      </c>
-      <c r="M116" t="s">
+        <v>206</v>
+      </c>
+      <c r="W116" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="117" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M117" t="s">
+    <row r="117" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W117" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="118" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="119" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M119" t="s">
+    <row r="119" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W119" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="120" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M120" t="s">
+    <row r="120" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W120" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="121" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="122" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="C122" t="s">
         <v>166</v>
       </c>
-      <c r="M122" t="s">
+      <c r="J122" t="s">
+        <v>263</v>
+      </c>
+      <c r="W122" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="123" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="124" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="C124" t="s">
         <v>176</v>
       </c>
@@ -1941,310 +2355,524 @@
         <v>188</v>
       </c>
       <c r="I124" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
+        <v>205</v>
+      </c>
+      <c r="L124" t="s">
+        <v>287</v>
+      </c>
+      <c r="M124" t="s">
+        <v>292</v>
+      </c>
+      <c r="P124" t="s">
+        <v>314</v>
+      </c>
+      <c r="R124" t="s">
+        <v>327</v>
+      </c>
+      <c r="S124" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="125" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="S125" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="126" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B126" t="s">
+    <row r="127" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B127" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="127" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M127" t="s">
+    <row r="128" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W128" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B128" t="s">
+    <row r="129" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B129" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="129" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M129" t="s">
+    <row r="130" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="C130" t="s">
+        <v>336</v>
+      </c>
+      <c r="W130" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="130" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M130" t="s">
+    <row r="131" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W131" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="131" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B131" t="s">
+    <row r="132" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B132" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="132" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M132" t="s">
+    <row r="133" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W133" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="133" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M133" t="s">
+    <row r="134" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W134" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="134" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B134" t="s">
+    <row r="135" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B135" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="135" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="C135" t="s">
+    <row r="136" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="C136" t="s">
         <v>167</v>
       </c>
-      <c r="D135" t="s">
+      <c r="D136" t="s">
         <v>185</v>
       </c>
-      <c r="E135" t="s">
+      <c r="E136" t="s">
         <v>189</v>
       </c>
-      <c r="F135" t="s">
+      <c r="F136" t="s">
         <v>193</v>
       </c>
-      <c r="G135" t="s">
+      <c r="G136" t="s">
         <v>198</v>
       </c>
-      <c r="H135" t="s">
+      <c r="H136" t="s">
         <v>202</v>
       </c>
-      <c r="I135" t="s">
-        <v>210</v>
-      </c>
-      <c r="M135" t="s">
+      <c r="I136" t="s">
+        <v>208</v>
+      </c>
+      <c r="J136" t="s">
+        <v>264</v>
+      </c>
+      <c r="K136" t="s">
+        <v>279</v>
+      </c>
+      <c r="L136" t="s">
+        <v>286</v>
+      </c>
+      <c r="M136" t="s">
+        <v>293</v>
+      </c>
+      <c r="N136" t="s">
+        <v>303</v>
+      </c>
+      <c r="O136" t="s">
+        <v>304</v>
+      </c>
+      <c r="P136" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>341</v>
+      </c>
+      <c r="R136" t="s">
+        <v>325</v>
+      </c>
+      <c r="S136" t="s">
+        <v>331</v>
+      </c>
+      <c r="T136" t="s">
+        <v>332</v>
+      </c>
+      <c r="W136" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="136" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="C136" t="s">
+    <row r="137" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="C137" t="s">
         <v>168</v>
       </c>
-      <c r="F136" t="s">
+      <c r="F137" t="s">
         <v>192</v>
       </c>
-      <c r="I136" t="s">
+      <c r="I137" t="s">
+        <v>209</v>
+      </c>
+      <c r="J137" t="s">
+        <v>265</v>
+      </c>
+      <c r="M137" t="s">
+        <v>294</v>
+      </c>
+      <c r="O137" t="s">
+        <v>305</v>
+      </c>
+      <c r="S137" t="s">
+        <v>319</v>
+      </c>
+      <c r="T137" t="s">
+        <v>333</v>
+      </c>
+      <c r="W137" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="138" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="C138" t="s">
+        <v>169</v>
+      </c>
+      <c r="J138" t="s">
+        <v>266</v>
+      </c>
+      <c r="O138" t="s">
+        <v>306</v>
+      </c>
+      <c r="S138" t="s">
+        <v>320</v>
+      </c>
+      <c r="T138" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="139" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="J139" t="s">
+        <v>267</v>
+      </c>
+      <c r="O139" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="140" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B141" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="142" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W142" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="143" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B143" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="144" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="J144" t="s">
+        <v>268</v>
+      </c>
+      <c r="W144" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="145" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W145" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="146" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B146" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="147" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W147" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="148" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B148" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="149" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="W149" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="150" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B150" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="151" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B151" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="152" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B152" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="153" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C153" t="s">
+        <v>337</v>
+      </c>
+      <c r="D153" t="s">
+        <v>339</v>
+      </c>
+      <c r="G153" t="s">
+        <v>340</v>
+      </c>
+      <c r="J153" t="s">
+        <v>269</v>
+      </c>
+      <c r="K153" t="s">
+        <v>280</v>
+      </c>
+      <c r="M153" t="s">
+        <v>295</v>
+      </c>
+      <c r="N153" t="s">
+        <v>308</v>
+      </c>
+      <c r="O153" t="s">
+        <v>311</v>
+      </c>
+      <c r="P153" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="154" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C154" t="s">
+        <v>338</v>
+      </c>
+      <c r="J154" t="s">
+        <v>270</v>
+      </c>
+      <c r="O154" t="s">
+        <v>312</v>
+      </c>
+      <c r="P154" t="s">
+        <v>323</v>
+      </c>
+      <c r="W154" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="155" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="J155" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="156" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
         <v>211</v>
       </c>
-      <c r="M136" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="137" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="C137" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="139" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B139" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="140" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M140" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="141" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B141" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="142" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M142" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="143" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M143" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="144" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B144" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="145" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M145" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="146" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B146" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="147" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="M147" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="148" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B148" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="149" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B149" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="150" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B150" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
+    </row>
+    <row r="157" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B157" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="158" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="D158" t="s">
+        <v>219</v>
+      </c>
+      <c r="E158" t="s">
+        <v>222</v>
+      </c>
+      <c r="M158" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="159" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B159" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="160" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="C160" t="s">
+        <v>215</v>
+      </c>
+      <c r="D160" t="s">
+        <v>220</v>
+      </c>
+      <c r="G160" t="s">
+        <v>225</v>
+      </c>
+      <c r="I160" t="s">
+        <v>227</v>
+      </c>
+      <c r="J160" t="s">
+        <v>272</v>
+      </c>
+      <c r="M160" t="s">
+        <v>298</v>
+      </c>
+      <c r="S160" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="C161" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="162" spans="1:17" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B162" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="152" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B152" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="153" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="D153" t="s">
-        <v>222</v>
-      </c>
-      <c r="E153" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="154" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B154" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="155" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="C155" t="s">
+    <row r="163" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="C163" t="s">
+        <v>217</v>
+      </c>
+      <c r="D163" t="s">
+        <v>221</v>
+      </c>
+      <c r="E163" t="s">
+        <v>223</v>
+      </c>
+      <c r="F163" t="s">
+        <v>224</v>
+      </c>
+      <c r="H163" t="s">
+        <v>226</v>
+      </c>
+      <c r="I163" t="s">
+        <v>228</v>
+      </c>
+      <c r="J163" t="s">
+        <v>276</v>
+      </c>
+      <c r="K163" t="s">
+        <v>282</v>
+      </c>
+      <c r="L163" t="s">
+        <v>288</v>
+      </c>
+      <c r="M163" t="s">
+        <v>296</v>
+      </c>
+      <c r="N163" t="s">
+        <v>309</v>
+      </c>
+      <c r="O163" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="C164" t="s">
         <v>218</v>
       </c>
-      <c r="D155" t="s">
-        <v>223</v>
-      </c>
-      <c r="G155" t="s">
-        <v>228</v>
-      </c>
-      <c r="I155" t="s">
+      <c r="I164" t="s">
+        <v>229</v>
+      </c>
+      <c r="L164" t="s">
+        <v>289</v>
+      </c>
+      <c r="M164" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q164" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="I165" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="156" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="C156" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="157" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B157" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="158" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="C158" t="s">
-        <v>220</v>
-      </c>
-      <c r="D158" t="s">
-        <v>224</v>
-      </c>
-      <c r="E158" t="s">
-        <v>226</v>
-      </c>
-      <c r="F158" t="s">
-        <v>227</v>
-      </c>
-      <c r="H158" t="s">
-        <v>229</v>
-      </c>
-      <c r="I158" t="s">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="159" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="C159" t="s">
-        <v>221</v>
-      </c>
-      <c r="I159" t="s">
+    <row r="167" spans="1:17" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B167" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="160" spans="1:13" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="I160" t="s">
+    <row r="168" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="C168" t="s">
+        <v>237</v>
+      </c>
+      <c r="J168" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B169" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
+    <row r="170" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="C170" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="171" spans="1:17" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B171" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="162" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B162" t="s">
+    <row r="172" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="C172" t="s">
+        <v>239</v>
+      </c>
+      <c r="F172" t="s">
+        <v>241</v>
+      </c>
+      <c r="J172" t="s">
+        <v>273</v>
+      </c>
+      <c r="M172" t="s">
+        <v>300</v>
+      </c>
+      <c r="P172" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="173" spans="1:17" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B173" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="163" spans="1:6" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="C163" t="s">
+    <row r="174" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="C174" t="s">
+        <v>335</v>
+      </c>
+      <c r="J174" t="s">
+        <v>274</v>
+      </c>
+      <c r="K174" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="175" spans="1:17" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B175" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="176" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="C176" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="164" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B164" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="C165" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B166" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="C167" t="s">
-        <v>242</v>
-      </c>
-      <c r="F167" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B168" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="C169" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B170" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="C171" t="s">
-        <v>244</v>
+      <c r="K176" t="s">
+        <v>283</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="W154" r:id="rId1" xr:uid="{9A3B04D8-DEDC-498E-9A6D-F5470AE73780}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jarod\Desktop\sjarod.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AECE1B71-01DF-42D6-BEE1-0C2190A9A429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{271D2294-05A5-4F10-BC26-A7CB6ED76C93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{16C9B547-A0B7-45C0-B721-251715838CB6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{16C9B547-A0B7-45C0-B721-251715838CB6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="344">
   <si>
     <t>Game Programming 1</t>
   </si>
@@ -1062,6 +1062,12 @@
   </si>
   <si>
     <t>reunions entre equipiers et avec les producers</t>
+  </si>
+  <si>
+    <t>VFX Fluid</t>
+  </si>
+  <si>
+    <t>Mesh Shader Implementation</t>
   </si>
 </sst>
 </file>
@@ -1457,7 +1463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0FD204F-2399-4498-A879-12600FE66628}">
-  <dimension ref="A1:W176"/>
+  <dimension ref="A1:W178"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -2609,268 +2615,278 @@
     </row>
     <row r="152" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="153" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B153" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="154" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B154" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="153" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C153" t="s">
+    <row r="155" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C155" t="s">
         <v>337</v>
       </c>
-      <c r="D153" t="s">
+      <c r="D155" t="s">
         <v>339</v>
       </c>
-      <c r="G153" t="s">
+      <c r="G155" t="s">
         <v>340</v>
       </c>
-      <c r="J153" t="s">
+      <c r="J155" t="s">
         <v>269</v>
       </c>
-      <c r="K153" t="s">
+      <c r="K155" t="s">
         <v>280</v>
       </c>
-      <c r="M153" t="s">
+      <c r="M155" t="s">
         <v>295</v>
       </c>
-      <c r="N153" t="s">
+      <c r="N155" t="s">
         <v>308</v>
       </c>
-      <c r="O153" t="s">
+      <c r="O155" t="s">
         <v>311</v>
       </c>
-      <c r="P153" t="s">
+      <c r="P155" t="s">
         <v>316</v>
       </c>
-      <c r="Q153" t="s">
+      <c r="Q155" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="154" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="C154" t="s">
+    <row r="156" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C156" t="s">
         <v>338</v>
       </c>
-      <c r="J154" t="s">
+      <c r="J156" t="s">
         <v>270</v>
       </c>
-      <c r="O154" t="s">
+      <c r="O156" t="s">
         <v>312</v>
       </c>
-      <c r="P154" t="s">
+      <c r="P156" t="s">
         <v>323</v>
       </c>
-      <c r="W154" s="2" t="s">
+      <c r="W156" s="2" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="155" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="J155" t="s">
+    <row r="157" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="J157" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="156" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
+    <row r="158" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
         <v>211</v>
-      </c>
-    </row>
-    <row r="157" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B157" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="158" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="D158" t="s">
-        <v>219</v>
-      </c>
-      <c r="E158" t="s">
-        <v>222</v>
-      </c>
-      <c r="M158" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="159" spans="1:23" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B159" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="160" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="D160" t="s">
+        <v>219</v>
+      </c>
+      <c r="E160" t="s">
+        <v>222</v>
+      </c>
+      <c r="M160" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="161" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B161" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="160" spans="1:23" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="C160" t="s">
+    <row r="162" spans="1:19" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="C162" t="s">
         <v>215</v>
       </c>
-      <c r="D160" t="s">
+      <c r="D162" t="s">
         <v>220</v>
       </c>
-      <c r="G160" t="s">
+      <c r="G162" t="s">
         <v>225</v>
       </c>
-      <c r="I160" t="s">
+      <c r="I162" t="s">
         <v>227</v>
       </c>
-      <c r="J160" t="s">
+      <c r="J162" t="s">
         <v>272</v>
       </c>
-      <c r="M160" t="s">
+      <c r="M162" t="s">
         <v>298</v>
       </c>
-      <c r="S160" t="s">
+      <c r="S162" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="161" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="C161" t="s">
+    <row r="163" spans="1:19" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="C163" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="162" spans="1:17" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B162" t="s">
+    <row r="164" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B164" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="163" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="C163" t="s">
+    <row r="165" spans="1:19" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="C165" t="s">
         <v>217</v>
       </c>
-      <c r="D163" t="s">
+      <c r="D165" t="s">
         <v>221</v>
       </c>
-      <c r="E163" t="s">
+      <c r="E165" t="s">
         <v>223</v>
       </c>
-      <c r="F163" t="s">
+      <c r="F165" t="s">
         <v>224</v>
       </c>
-      <c r="H163" t="s">
+      <c r="H165" t="s">
         <v>226</v>
       </c>
-      <c r="I163" t="s">
+      <c r="I165" t="s">
         <v>228</v>
       </c>
-      <c r="J163" t="s">
+      <c r="J165" t="s">
         <v>276</v>
       </c>
-      <c r="K163" t="s">
+      <c r="K165" t="s">
         <v>282</v>
       </c>
-      <c r="L163" t="s">
+      <c r="L165" t="s">
         <v>288</v>
       </c>
-      <c r="M163" t="s">
+      <c r="M165" t="s">
         <v>296</v>
       </c>
-      <c r="N163" t="s">
+      <c r="N165" t="s">
         <v>309</v>
       </c>
-      <c r="O163" t="s">
+      <c r="O165" t="s">
         <v>317</v>
       </c>
-      <c r="Q163" t="s">
+      <c r="Q165" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="164" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="C164" t="s">
+    <row r="166" spans="1:19" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="C166" t="s">
         <v>218</v>
       </c>
-      <c r="I164" t="s">
+      <c r="I166" t="s">
         <v>229</v>
       </c>
-      <c r="L164" t="s">
+      <c r="L166" t="s">
         <v>289</v>
       </c>
-      <c r="M164" t="s">
+      <c r="M166" t="s">
         <v>297</v>
       </c>
-      <c r="Q164" t="s">
+      <c r="Q166" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="165" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="I165" t="s">
+    <row r="167" spans="1:19" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="I167" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
+    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="167" spans="1:17" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B167" t="s">
+    <row r="169" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B169" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="168" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="C168" t="s">
+    <row r="170" spans="1:19" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="C170" t="s">
         <v>237</v>
       </c>
-      <c r="J168" t="s">
+      <c r="J170" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="169" spans="1:17" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B169" t="s">
+    <row r="171" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B171" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="170" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="C170" t="s">
+    <row r="172" spans="1:19" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="C172" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="171" spans="1:17" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B171" t="s">
+    <row r="173" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B173" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="172" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="C172" t="s">
+    <row r="174" spans="1:19" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="C174" t="s">
         <v>239</v>
       </c>
-      <c r="F172" t="s">
+      <c r="F174" t="s">
         <v>241</v>
       </c>
-      <c r="J172" t="s">
+      <c r="J174" t="s">
         <v>273</v>
       </c>
-      <c r="M172" t="s">
+      <c r="M174" t="s">
         <v>300</v>
       </c>
-      <c r="P172" t="s">
+      <c r="P174" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="173" spans="1:17" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B173" t="s">
+    <row r="175" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B175" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="174" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="C174" t="s">
+    <row r="176" spans="1:19" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="C176" t="s">
         <v>335</v>
       </c>
-      <c r="J174" t="s">
+      <c r="J176" t="s">
         <v>274</v>
       </c>
-      <c r="K174" t="s">
+      <c r="K176" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="175" spans="1:17" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B175" t="s">
+    <row r="177" spans="2:11" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B177" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="176" spans="1:17" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="C176" t="s">
+    <row r="178" spans="2:11" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="C178" t="s">
         <v>240</v>
       </c>
-      <c r="K176" t="s">
+      <c r="K178" t="s">
         <v>283</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="W154" r:id="rId1" xr:uid="{9A3B04D8-DEDC-498E-9A6D-F5470AE73780}"/>
+    <hyperlink ref="W156" r:id="rId1" xr:uid="{9A3B04D8-DEDC-498E-9A6D-F5470AE73780}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
